--- a/All Sheets/2nd Sem.MOD.2025.xlsx
+++ b/All Sheets/2nd Sem.MOD.2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baby\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baby\Desktop\New folder\2nd Sem. MOD.2025\All Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9006B4C-2F28-461D-865E-1BA7A332A3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F603A30F-DD1A-489A-849B-7EAAD96D6530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="23" activeTab="24" xr2:uid="{567E6C58-DD92-4665-BCF5-9F4C172BD6C7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="24" activeTab="25" xr2:uid="{567E6C58-DD92-4665-BCF5-9F4C172BD6C7}"/>
   </bookViews>
   <sheets>
     <sheet name="2nd Sem.MOD.2025(Purposive Comm" sheetId="12" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="2nd Sem.MOD.2025(Human Computer" sheetId="26" r:id="rId23"/>
     <sheet name="2nd Sem.MOD.2025(GRAPHICS &amp; Vis" sheetId="27" r:id="rId24"/>
     <sheet name="2nd Sem.MOD.2025(Discrete St1&amp;2" sheetId="28" r:id="rId25"/>
+    <sheet name="2nd Sem.MOD.2025(The Contempora" sheetId="29" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="353">
   <si>
     <t>Opiniano, Rhealyn B.</t>
   </si>
@@ -842,9 +843,6 @@
     <t xml:space="preserve">                       Subject: Accounting 1</t>
   </si>
   <si>
-    <t xml:space="preserve">                       Subject: Subject: Accounting 1</t>
-  </si>
-  <si>
     <t>Abania,Krizia Jean S.</t>
   </si>
   <si>
@@ -1173,6 +1171,9 @@
   </si>
   <si>
     <t>Barliso,Richelle R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                       Subject: The Contemporary World</t>
   </si>
 </sst>
 </file>
@@ -4897,6 +4898,455 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1695450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Image result for metro business college logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6493DAD5-B454-41EA-AF49-1AAC097A4BB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="533400" y="0"/>
+          <a:ext cx="1466850" cy="1133475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1695450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Image result for metro business college logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63867F7F-4F0D-4011-840A-5641F3606996}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="533400" y="0"/>
+          <a:ext cx="1466850" cy="1133475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1695450</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Image result for metro business college logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C251AD5F-593E-43D6-A197-0F8FCF8DEB82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="533400" y="9001125"/>
+          <a:ext cx="1466850" cy="1133475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1695450</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="Image result for metro business college logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{690C72B0-3966-4D56-A687-9F9035694438}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="533400" y="9001125"/>
+          <a:ext cx="1466850" cy="1133475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1695450</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5" descr="Image result for metro business college logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4C6B460-CACC-4F3C-A8AF-5B64AE35717F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="533400" y="18002250"/>
+          <a:ext cx="1466850" cy="1133475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1695450</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="Image result for metro business college logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1943B706-10BF-489B-A803-F4C31967800D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="533400" y="18002250"/>
+          <a:ext cx="1466850" cy="1133475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -8060,7 +8510,7 @@
     <row r="7" spans="1:10" ht="15.75">
       <c r="A7" s="2"/>
       <c r="B7" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="9"/>
@@ -8204,7 +8654,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -8222,7 +8672,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -8778,7 +9228,7 @@
     <row r="52" spans="1:10" ht="15.75">
       <c r="A52" s="2"/>
       <c r="B52" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="9"/>
@@ -8904,7 +9354,7 @@
         <v>17</v>
       </c>
       <c r="B59" s="58" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -9401,7 +9851,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -9525,7 +9975,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -9931,7 +10381,7 @@
     </row>
     <row r="52" spans="1:10" ht="15.75">
       <c r="B52" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D52" s="9"/>
       <c r="G52" s="9" t="s">
@@ -10019,7 +10469,7 @@
         <v>17</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -10426,7 +10876,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -10503,7 +10953,7 @@
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -10521,7 +10971,7 @@
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -10539,7 +10989,7 @@
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -10557,7 +11007,7 @@
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -10575,7 +11025,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -10593,7 +11043,7 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -10604,14 +11054,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -10622,14 +11072,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -10647,7 +11097,7 @@
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
@@ -10665,7 +11115,7 @@
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
@@ -10701,7 +11151,7 @@
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
       <c r="G24" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
@@ -10719,7 +11169,7 @@
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -10755,7 +11205,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -10956,7 +11406,7 @@
     </row>
     <row r="52" spans="1:10" ht="15.75">
       <c r="B52" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D52" s="9"/>
       <c r="G52" s="9" t="s">
@@ -11026,14 +11476,14 @@
         <v>16</v>
       </c>
       <c r="B58" s="62" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
       <c r="F58" s="17"/>
       <c r="G58" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
@@ -11051,7 +11501,7 @@
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
       <c r="G59" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
@@ -11069,7 +11519,7 @@
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
       <c r="G60" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
@@ -11087,7 +11537,7 @@
       <c r="E61" s="17"/>
       <c r="F61" s="17"/>
       <c r="G61" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
@@ -11123,7 +11573,7 @@
       <c r="E63" s="17"/>
       <c r="F63" s="17"/>
       <c r="G63" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="17"/>
@@ -11141,7 +11591,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H64" s="17"/>
       <c r="I64" s="17"/>
@@ -11152,14 +11602,14 @@
         <v>23</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H65" s="17"/>
       <c r="I65" s="17"/>
@@ -11170,14 +11620,14 @@
         <v>24</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H66" s="17"/>
       <c r="I66" s="17"/>
@@ -11195,7 +11645,7 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H67" s="17"/>
       <c r="I67" s="17"/>
@@ -11206,14 +11656,14 @@
         <v>26</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H68" s="17"/>
       <c r="I68" s="17"/>
@@ -11224,14 +11674,14 @@
         <v>27</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H69" s="17"/>
       <c r="I69" s="17"/>
@@ -11249,7 +11699,7 @@
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
       <c r="G70" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
@@ -11267,7 +11717,7 @@
       <c r="E71" s="17"/>
       <c r="F71" s="17"/>
       <c r="G71" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17"/>
@@ -11285,7 +11735,7 @@
       <c r="E72" s="17"/>
       <c r="F72" s="17"/>
       <c r="G72" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="17"/>
@@ -11486,7 +11936,7 @@
     </row>
     <row r="97" spans="1:10" ht="15.75">
       <c r="B97" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D97" s="9"/>
       <c r="G97" s="9" t="s">
@@ -11563,7 +12013,7 @@
       <c r="E103" s="17"/>
       <c r="F103" s="17"/>
       <c r="G103" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="17"/>
@@ -11574,14 +12024,14 @@
         <v>32</v>
       </c>
       <c r="B104" s="39" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C104" s="17"/>
       <c r="D104" s="17"/>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
       <c r="G104" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="17"/>
@@ -11592,14 +12042,14 @@
         <v>33</v>
       </c>
       <c r="B105" s="39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
       <c r="G105" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H105" s="17"/>
       <c r="I105" s="17"/>
@@ -11617,7 +12067,7 @@
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
       <c r="G106" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H106" s="17"/>
       <c r="I106" s="17"/>
@@ -11635,7 +12085,7 @@
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
       <c r="G107" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H107" s="17"/>
       <c r="I107" s="17"/>
@@ -11646,7 +12096,7 @@
         <v>36</v>
       </c>
       <c r="B108" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
@@ -11987,7 +12437,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -12093,7 +12543,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -12309,7 +12759,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -12605,7 +13055,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -12675,14 +13125,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -12700,7 +13150,7 @@
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -12711,14 +13161,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -12729,14 +13179,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -12747,7 +13197,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -12765,14 +13215,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -12783,14 +13233,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -13157,7 +13607,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -13227,14 +13677,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -13245,14 +13695,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -13263,14 +13713,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -13281,14 +13731,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -13299,14 +13749,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -13317,14 +13767,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -13335,14 +13785,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -13353,14 +13803,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -13715,7 +14165,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -13792,7 +14242,7 @@
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -13810,7 +14260,7 @@
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -13828,7 +14278,7 @@
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -13846,7 +14296,7 @@
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -13864,7 +14314,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -13882,7 +14332,7 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -13893,14 +14343,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -13911,14 +14361,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -13936,7 +14386,7 @@
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
@@ -13954,7 +14404,7 @@
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
@@ -13972,7 +14422,7 @@
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
       <c r="G23" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
@@ -13990,7 +14440,7 @@
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
       <c r="G24" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
@@ -14001,14 +14451,14 @@
         <v>13</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -14019,14 +14469,14 @@
         <v>14</v>
       </c>
       <c r="B26" s="63" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
@@ -14044,7 +14494,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -14245,7 +14695,7 @@
     </row>
     <row r="52" spans="1:10" ht="15.75">
       <c r="B52" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D52" s="9"/>
       <c r="G52" s="9" t="s">
@@ -14322,7 +14772,7 @@
       <c r="E58" s="17"/>
       <c r="F58" s="17"/>
       <c r="G58" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
@@ -14340,7 +14790,7 @@
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
       <c r="G59" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
@@ -14376,7 +14826,7 @@
       <c r="E61" s="17"/>
       <c r="F61" s="17"/>
       <c r="G61" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
@@ -14387,14 +14837,14 @@
         <v>20</v>
       </c>
       <c r="B62" s="63" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
       <c r="E62" s="17"/>
       <c r="F62" s="17"/>
       <c r="G62" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H62" s="17"/>
       <c r="I62" s="17"/>
@@ -14405,14 +14855,14 @@
         <v>21</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
       <c r="E63" s="17"/>
       <c r="F63" s="17"/>
       <c r="G63" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="17"/>
@@ -14423,14 +14873,14 @@
         <v>22</v>
       </c>
       <c r="B64" s="63" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H64" s="17"/>
       <c r="I64" s="17"/>
@@ -14448,7 +14898,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H65" s="17"/>
       <c r="I65" s="17"/>
@@ -14459,14 +14909,14 @@
         <v>24</v>
       </c>
       <c r="B66" s="63" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H66" s="17"/>
       <c r="I66" s="17"/>
@@ -14495,14 +14945,14 @@
         <v>26</v>
       </c>
       <c r="B68" s="63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H68" s="17"/>
       <c r="I68" s="17"/>
@@ -14520,7 +14970,7 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H69" s="17"/>
       <c r="I69" s="17"/>
@@ -14538,7 +14988,7 @@
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
       <c r="G70" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
@@ -14556,7 +15006,7 @@
       <c r="E71" s="17"/>
       <c r="F71" s="17"/>
       <c r="G71" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17"/>
@@ -14574,7 +15024,7 @@
       <c r="E72" s="17"/>
       <c r="F72" s="17"/>
       <c r="G72" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="17"/>
@@ -14775,7 +15225,7 @@
     </row>
     <row r="97" spans="1:10" ht="15.75">
       <c r="B97" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D97" s="9"/>
       <c r="G97" s="9" t="s">
@@ -14845,14 +15295,14 @@
         <v>31</v>
       </c>
       <c r="B103" s="63" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C103" s="17"/>
       <c r="D103" s="17"/>
       <c r="E103" s="17"/>
       <c r="F103" s="17"/>
       <c r="G103" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="17"/>
@@ -14863,14 +15313,14 @@
         <v>32</v>
       </c>
       <c r="B104" s="63" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C104" s="17"/>
       <c r="D104" s="17"/>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
       <c r="G104" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="17"/>
@@ -14888,7 +15338,7 @@
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
       <c r="G105" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H105" s="17"/>
       <c r="I105" s="17"/>
@@ -14906,7 +15356,7 @@
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
       <c r="G106" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H106" s="17"/>
       <c r="I106" s="17"/>
@@ -14917,7 +15367,7 @@
         <v>35</v>
       </c>
       <c r="B107" s="63" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
@@ -15270,7 +15720,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -15340,14 +15790,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -15365,7 +15815,7 @@
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -15376,14 +15826,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -15394,14 +15844,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -15412,14 +15862,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -15437,7 +15887,7 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -15448,14 +15898,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -15822,7 +16272,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -15892,7 +16342,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -15910,7 +16360,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -16344,7 +16794,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -16414,14 +16864,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -16439,7 +16889,7 @@
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -16450,14 +16900,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -16468,14 +16918,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -16486,7 +16936,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -16504,14 +16954,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -16522,14 +16972,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -16896,7 +17346,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -16966,14 +17416,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -16984,14 +17434,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -17002,14 +17452,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -17020,14 +17470,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -17038,14 +17488,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -17056,14 +17506,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -17074,14 +17524,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -17092,14 +17542,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -17454,7 +17904,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="48" t="s">
@@ -17531,7 +17981,7 @@
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -17549,7 +17999,7 @@
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="49" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -17567,7 +18017,7 @@
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="49" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -17585,7 +18035,7 @@
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -17603,7 +18053,7 @@
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="49" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -17621,7 +18071,7 @@
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -17632,14 +18082,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -17650,14 +18100,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -17675,7 +18125,7 @@
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
       <c r="G21" s="49" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
@@ -17693,7 +18143,7 @@
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
       <c r="G22" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
@@ -17711,7 +18161,7 @@
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
       <c r="G23" s="49" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
@@ -17729,7 +18179,7 @@
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
       <c r="G24" s="49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
@@ -17747,7 +18197,7 @@
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="49" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -17765,7 +18215,7 @@
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
@@ -17783,7 +18233,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -17979,7 +18429,7 @@
     </row>
     <row r="52" spans="1:10" ht="15.75">
       <c r="B52" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D52" s="9"/>
       <c r="G52" s="48" t="s">
@@ -18056,7 +18506,7 @@
       <c r="E58" s="17"/>
       <c r="F58" s="17"/>
       <c r="G58" s="41" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
@@ -18092,7 +18542,7 @@
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
       <c r="G60" s="41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
@@ -18128,7 +18578,7 @@
       <c r="E62" s="17"/>
       <c r="F62" s="17"/>
       <c r="G62" s="41" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H62" s="17"/>
       <c r="I62" s="17"/>
@@ -18164,7 +18614,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="41" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H64" s="17"/>
       <c r="I64" s="17"/>
@@ -18175,14 +18625,14 @@
         <v>23</v>
       </c>
       <c r="B65" s="51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="41" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H65" s="17"/>
       <c r="I65" s="17"/>
@@ -18193,7 +18643,7 @@
         <v>24</v>
       </c>
       <c r="B66" s="51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
@@ -18211,14 +18661,14 @@
         <v>25</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C67" s="17"/>
       <c r="D67" s="17"/>
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H67" s="17"/>
       <c r="I67" s="17"/>
@@ -18236,7 +18686,7 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="41" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H68" s="17"/>
       <c r="I68" s="17"/>
@@ -18247,14 +18697,14 @@
         <v>27</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H69" s="17"/>
       <c r="I69" s="17"/>
@@ -18272,7 +18722,7 @@
       <c r="E70" s="17"/>
       <c r="F70" s="17"/>
       <c r="G70" s="41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
@@ -18290,7 +18740,7 @@
       <c r="E71" s="17"/>
       <c r="F71" s="17"/>
       <c r="G71" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17"/>
@@ -18308,7 +18758,7 @@
       <c r="E72" s="17"/>
       <c r="F72" s="17"/>
       <c r="G72" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H72" s="17"/>
       <c r="I72" s="17"/>
@@ -18504,7 +18954,7 @@
     </row>
     <row r="97" spans="1:10" ht="15.75">
       <c r="B97" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D97" s="9"/>
       <c r="G97" s="48" t="s">
@@ -18581,7 +19031,7 @@
       <c r="E103" s="17"/>
       <c r="F103" s="17"/>
       <c r="G103" s="49" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="17"/>
@@ -18592,14 +19042,14 @@
         <v>32</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C104" s="17"/>
       <c r="D104" s="17"/>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
       <c r="G104" s="49" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H104" s="17"/>
       <c r="I104" s="17"/>
@@ -18610,14 +19060,14 @@
         <v>33</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
       <c r="G105" s="49" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H105" s="17"/>
       <c r="I105" s="17"/>
@@ -18628,14 +19078,14 @@
         <v>34</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
       <c r="G106" s="49" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H106" s="17"/>
       <c r="I106" s="17"/>
@@ -18653,7 +19103,7 @@
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
       <c r="G107" s="49" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H107" s="17"/>
       <c r="I107" s="17"/>
@@ -18671,7 +19121,7 @@
       <c r="E108" s="31"/>
       <c r="F108" s="31"/>
       <c r="G108" s="53" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H108" s="31"/>
       <c r="I108" s="31"/>
@@ -18682,7 +19132,7 @@
         <v>37</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -19009,7 +19459,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -19079,14 +19529,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -19097,14 +19547,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -19115,14 +19565,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -19133,14 +19583,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -19151,14 +19601,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -19169,14 +19619,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -19187,14 +19637,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -19205,14 +19655,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -19567,7 +20017,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -19637,14 +20087,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -19655,14 +20105,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -19673,14 +20123,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -19691,14 +20141,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -19709,14 +20159,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -19727,14 +20177,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -19745,14 +20195,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -19763,14 +20213,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -20125,7 +20575,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -20195,14 +20645,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -20213,14 +20663,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -20231,14 +20681,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -20249,14 +20699,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -20267,14 +20717,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -20285,14 +20735,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -20303,14 +20753,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -20321,14 +20771,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -20683,7 +21133,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -20753,14 +21203,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -20771,14 +21221,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -20789,14 +21239,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -20807,14 +21257,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -20825,14 +21275,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -20843,14 +21293,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -20861,14 +21311,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -20879,14 +21329,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -21241,7 +21691,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -21311,14 +21761,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -21329,14 +21779,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -21347,14 +21797,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -21365,14 +21815,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -21383,14 +21833,14 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
       <c r="F17" s="17"/>
       <c r="G17" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
@@ -21401,14 +21851,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -21419,14 +21869,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -21437,14 +21887,14 @@
         <v>8</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="17"/>
       <c r="G20" s="21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
@@ -21799,7 +22249,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="9" t="s">
@@ -21885,14 +22335,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -21903,14 +22353,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="63" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -21921,14 +22371,14 @@
         <v>3</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="17"/>
       <c r="G15" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
@@ -21939,14 +22389,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="63" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="17"/>
       <c r="G16" s="21" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
@@ -21957,7 +22407,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -21975,14 +22425,14 @@
         <v>6</v>
       </c>
       <c r="B18" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="17"/>
       <c r="G18" s="21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H18" s="17"/>
       <c r="I18" s="17"/>
@@ -21993,14 +22443,14 @@
         <v>7</v>
       </c>
       <c r="B19" s="63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
       <c r="G19" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
@@ -22323,6 +22773,1576 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B13:G19">
     <sortCondition ref="B13:B19"/>
   </sortState>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62F366F-8046-43EA-9F25-B12B96AE9671}">
+  <dimension ref="A2:J135"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" style="19" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" ht="27">
+      <c r="B2" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18">
+      <c r="B3" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75">
+      <c r="B6" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75">
+      <c r="B7" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="G7" s="48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75">
+      <c r="B8" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="G8" s="48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75">
+      <c r="B9" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75">
+      <c r="B10" s="7"/>
+      <c r="D10" s="23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="18">
+      <c r="B11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="25.5">
+      <c r="A12" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="15">
+        <v>1</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="15">
+        <v>2</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="49" t="s">
+        <v>268</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="15">
+        <v>3</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="15">
+        <v>4</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="15">
+        <v>5</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="15">
+        <v>6</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="49" t="s">
+        <v>272</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="15">
+        <v>7</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="15">
+        <v>8</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="15">
+        <v>9</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="15">
+        <v>10</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="15">
+        <v>11</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="49" t="s">
+        <v>276</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="15">
+        <v>12</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="15">
+        <v>13</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="15">
+        <v>14</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="15">
+        <v>15</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75">
+      <c r="B32" s="24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75">
+      <c r="B33" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="B34" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="B35" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="B36" s="26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="B37" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="G38" s="50"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="G39" s="50"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="50"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="G41" s="50"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="G42" s="50"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="G43" s="50"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="47" spans="1:9" ht="27">
+      <c r="B47" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="18">
+      <c r="B48" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="8"/>
+    </row>
+    <row r="51" spans="1:10" ht="15.75">
+      <c r="B51" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.75">
+      <c r="B52" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="G52" s="48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15.75">
+      <c r="B53" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="G53" s="48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15.75">
+      <c r="B54" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15.75">
+      <c r="B55" s="7"/>
+      <c r="D55" s="23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="18">
+      <c r="B56" s="7"/>
+      <c r="D56" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="25.5">
+      <c r="A57" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="15">
+        <v>16</v>
+      </c>
+      <c r="B58" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="15">
+        <v>17</v>
+      </c>
+      <c r="B59" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="15">
+        <v>18</v>
+      </c>
+      <c r="B60" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="15">
+        <v>19</v>
+      </c>
+      <c r="B61" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="15">
+        <v>20</v>
+      </c>
+      <c r="B62" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="15">
+        <v>21</v>
+      </c>
+      <c r="B63" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="15">
+        <v>22</v>
+      </c>
+      <c r="B64" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="41" t="s">
+        <v>283</v>
+      </c>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="15">
+        <v>23</v>
+      </c>
+      <c r="B65" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="3"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="15">
+        <v>24</v>
+      </c>
+      <c r="B66" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="41" t="s">
+        <v>285</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="15">
+        <v>25</v>
+      </c>
+      <c r="B67" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="3"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="15">
+        <v>26</v>
+      </c>
+      <c r="B68" s="45" t="s">
+        <v>310</v>
+      </c>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="3"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="15">
+        <v>27</v>
+      </c>
+      <c r="B69" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="15">
+        <v>28</v>
+      </c>
+      <c r="B70" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="3"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="15">
+        <v>29</v>
+      </c>
+      <c r="B71" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="3"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="15">
+        <v>30</v>
+      </c>
+      <c r="B72" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="3"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="34"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="4"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="34"/>
+      <c r="B74" s="35"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="4"/>
+    </row>
+    <row r="77" spans="1:10" ht="15.75">
+      <c r="B77" s="24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15.75">
+      <c r="B78" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F78" s="25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="B79" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F79" s="27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="B80" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="B81" s="26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="B82" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F82" s="27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="5"/>
+      <c r="B83" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="G83" s="50"/>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="5"/>
+      <c r="B84" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="G84" s="50"/>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="5"/>
+      <c r="B85" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="G85" s="50"/>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="5"/>
+      <c r="B86" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="G86" s="50"/>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="5"/>
+      <c r="B87" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="G87" s="50"/>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="5"/>
+      <c r="B88" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="G88" s="50"/>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="5"/>
+      <c r="B89" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="5"/>
+      <c r="B90" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="22"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+    </row>
+    <row r="92" spans="1:9" ht="27">
+      <c r="B92" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="18">
+      <c r="B93" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C93" s="8"/>
+    </row>
+    <row r="96" spans="1:9" ht="15.75">
+      <c r="B96" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="15.75">
+      <c r="B97" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D97" s="9"/>
+      <c r="G97" s="48" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="15.75">
+      <c r="B98" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" s="9"/>
+      <c r="G98" s="48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="15.75">
+      <c r="B99" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="15.75">
+      <c r="B100" s="7"/>
+      <c r="D100" s="23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="18">
+      <c r="B101" s="7"/>
+      <c r="D101" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="25.5">
+      <c r="A102" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G102" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I102" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="15">
+        <v>31</v>
+      </c>
+      <c r="B103" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C103" s="17"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17"/>
+      <c r="G103" s="49" t="s">
+        <v>290</v>
+      </c>
+      <c r="H103" s="17"/>
+      <c r="I103" s="17"/>
+      <c r="J103" s="3"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="15">
+        <v>32</v>
+      </c>
+      <c r="B104" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="17"/>
+      <c r="D104" s="17"/>
+      <c r="E104" s="17"/>
+      <c r="F104" s="17"/>
+      <c r="G104" s="49" t="s">
+        <v>291</v>
+      </c>
+      <c r="H104" s="17"/>
+      <c r="I104" s="17"/>
+      <c r="J104" s="3"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="15">
+        <v>33</v>
+      </c>
+      <c r="B105" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="17"/>
+      <c r="D105" s="17"/>
+      <c r="E105" s="17"/>
+      <c r="F105" s="17"/>
+      <c r="G105" s="49" t="s">
+        <v>292</v>
+      </c>
+      <c r="H105" s="17"/>
+      <c r="I105" s="17"/>
+      <c r="J105" s="3"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="15">
+        <v>34</v>
+      </c>
+      <c r="B106" s="45" t="s">
+        <v>306</v>
+      </c>
+      <c r="C106" s="17"/>
+      <c r="D106" s="17"/>
+      <c r="E106" s="17"/>
+      <c r="F106" s="17"/>
+      <c r="G106" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="H106" s="17"/>
+      <c r="I106" s="17"/>
+      <c r="J106" s="3"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="15">
+        <v>35</v>
+      </c>
+      <c r="B107" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107" s="17"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="17"/>
+      <c r="F107" s="17"/>
+      <c r="G107" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="H107" s="17"/>
+      <c r="I107" s="17"/>
+      <c r="J107" s="3"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="15">
+        <v>36</v>
+      </c>
+      <c r="B108" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="C108" s="17"/>
+      <c r="D108" s="17"/>
+      <c r="E108" s="17"/>
+      <c r="F108" s="17"/>
+      <c r="G108" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="H108" s="17"/>
+      <c r="I108" s="17"/>
+      <c r="J108" s="3"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="15">
+        <v>37</v>
+      </c>
+      <c r="B109" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="17"/>
+      <c r="D109" s="17"/>
+      <c r="E109" s="17"/>
+      <c r="F109" s="17"/>
+      <c r="G109" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="H109" s="17"/>
+      <c r="I109" s="17"/>
+      <c r="J109" s="3"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="15">
+        <v>38</v>
+      </c>
+      <c r="B110" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="17"/>
+      <c r="D110" s="17"/>
+      <c r="E110" s="17"/>
+      <c r="F110" s="17"/>
+      <c r="G110" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="H110" s="17"/>
+      <c r="I110" s="17"/>
+      <c r="J110" s="3"/>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="29">
+        <v>39</v>
+      </c>
+      <c r="B111" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="C111" s="31"/>
+      <c r="D111" s="31"/>
+      <c r="E111" s="31"/>
+      <c r="F111" s="31"/>
+      <c r="G111" s="53" t="s">
+        <v>317</v>
+      </c>
+      <c r="H111" s="31"/>
+      <c r="I111" s="31"/>
+      <c r="J111" s="33"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="15">
+        <v>40</v>
+      </c>
+      <c r="B112" s="45" t="s">
+        <v>307</v>
+      </c>
+      <c r="C112" s="17"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="17"/>
+      <c r="G112" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H112" s="17"/>
+      <c r="I112" s="17"/>
+      <c r="J112" s="3"/>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="34"/>
+      <c r="B113" s="59"/>
+      <c r="C113" s="36"/>
+      <c r="D113" s="36"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36"/>
+      <c r="G113" s="55"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36"/>
+      <c r="J113" s="4"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="34"/>
+      <c r="B114" s="59"/>
+      <c r="C114" s="36"/>
+      <c r="D114" s="36"/>
+      <c r="E114" s="36"/>
+      <c r="F114" s="36"/>
+      <c r="G114" s="55"/>
+      <c r="H114" s="36"/>
+      <c r="I114" s="36"/>
+      <c r="J114" s="4"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="34"/>
+      <c r="B115" s="59"/>
+      <c r="C115" s="36"/>
+      <c r="D115" s="36"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="36"/>
+      <c r="G115" s="55"/>
+      <c r="H115" s="36"/>
+      <c r="I115" s="36"/>
+      <c r="J115" s="4"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" s="34"/>
+      <c r="B116" s="59"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+      <c r="G116" s="55"/>
+      <c r="H116" s="36"/>
+      <c r="I116" s="36"/>
+      <c r="J116" s="4"/>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="34"/>
+      <c r="B117" s="59"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+      <c r="G117" s="55"/>
+      <c r="H117" s="36"/>
+      <c r="I117" s="36"/>
+      <c r="J117" s="4"/>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="34"/>
+      <c r="B118" s="54"/>
+      <c r="C118" s="36"/>
+      <c r="D118" s="36"/>
+      <c r="E118" s="36"/>
+      <c r="F118" s="36"/>
+      <c r="G118" s="55"/>
+      <c r="H118" s="36"/>
+      <c r="I118" s="36"/>
+      <c r="J118" s="4"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="34"/>
+      <c r="B119" s="54"/>
+      <c r="C119" s="56"/>
+      <c r="D119" s="56"/>
+      <c r="E119" s="56"/>
+      <c r="F119" s="56"/>
+      <c r="G119" s="37"/>
+      <c r="H119" s="56"/>
+      <c r="I119" s="56"/>
+      <c r="J119" s="57"/>
+    </row>
+    <row r="122" spans="1:10" ht="15.75">
+      <c r="B122" s="24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="15.75">
+      <c r="B123" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F123" s="25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="B124" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F124" s="27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="B125" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="B126" s="26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="B127" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F127" s="27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" s="5"/>
+      <c r="B128" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="G128" s="50"/>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="5"/>
+      <c r="B129" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="G129" s="50"/>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="5"/>
+      <c r="B130" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="G130" s="50"/>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="5"/>
+      <c r="B131" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="G131" s="50"/>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="5"/>
+      <c r="B132" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="G132" s="50"/>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="5"/>
+      <c r="B133" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="G133" s="50"/>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="5"/>
+      <c r="B134" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
+      <c r="G134" s="22"/>
+      <c r="H134" s="4"/>
+      <c r="I134" s="4"/>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="5"/>
+      <c r="B135" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="22"/>
+      <c r="H135" s="4"/>
+      <c r="I135" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -22370,7 +24390,7 @@
     </row>
     <row r="7" spans="1:10" ht="15.75">
       <c r="B7" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D7" s="9"/>
       <c r="G7" s="48" t="s">
@@ -22895,7 +24915,7 @@
     </row>
     <row r="52" spans="1:10" ht="15.75">
       <c r="B52" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D52" s="9"/>
       <c r="G52" s="48" t="s">
@@ -23001,7 +25021,7 @@
         <v>18</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
@@ -23420,7 +25440,7 @@
     </row>
     <row r="97" spans="1:10" ht="15.75">
       <c r="B97" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D97" s="9"/>
       <c r="G97" s="48" t="s">
@@ -24037,7 +26057,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -24055,14 +26075,14 @@
         <v>2</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="49" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
@@ -24242,7 +26262,7 @@
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
       <c r="G24" s="49" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
@@ -24296,7 +26316,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="49" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -24492,7 +26512,7 @@
     </row>
     <row r="52" spans="1:10" ht="15.75">
       <c r="B52" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D52" s="9"/>
       <c r="G52" s="48" t="s">
@@ -24580,14 +26600,14 @@
         <v>17</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
       <c r="G59" s="41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
@@ -24598,14 +26618,14 @@
         <v>18</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
       <c r="G60" s="41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
@@ -24616,14 +26636,14 @@
         <v>19</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
       <c r="F61" s="17"/>
       <c r="G61" s="41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
@@ -24652,7 +26672,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
@@ -25141,7 +27161,7 @@
         <v>34</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
@@ -25195,7 +27215,7 @@
         <v>37</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -25346,7 +27366,7 @@
       <c r="E117" s="17"/>
       <c r="F117" s="17"/>
       <c r="G117" s="49" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H117" s="17"/>
       <c r="I117" s="17"/>
